--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113610417</v>
       </c>
       <c r="B2" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>113610418</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113610429</v>
+        <v>113610419</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396209</v>
+        <v>395926</v>
       </c>
       <c r="R4" t="n">
-        <v>7063727</v>
+        <v>7063563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113610425</v>
+        <v>113610420</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396148</v>
+        <v>395875</v>
       </c>
       <c r="R5" t="n">
-        <v>7063685</v>
+        <v>7063522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113610431</v>
+        <v>113610421</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396351</v>
+        <v>395880</v>
       </c>
       <c r="R6" t="n">
-        <v>7063751</v>
+        <v>7063472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113610428</v>
+        <v>113610422</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396178</v>
+        <v>395786</v>
       </c>
       <c r="R7" t="n">
-        <v>7063722</v>
+        <v>7063549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113610424</v>
+        <v>113610423</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>395872</v>
+        <v>395853</v>
       </c>
       <c r="R8" t="n">
-        <v>7063713</v>
+        <v>7063695</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113610420</v>
+        <v>113610424</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>395875</v>
+        <v>395872</v>
       </c>
       <c r="R9" t="n">
-        <v>7063522</v>
+        <v>7063713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,15 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113610422</v>
+        <v>113610425</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>395786</v>
+        <v>396148</v>
       </c>
       <c r="R10" t="n">
-        <v>7063549</v>
+        <v>7063685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,12 +1591,7 @@
         <v>113610426</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113610423</v>
+        <v>113610427</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>395853</v>
+        <v>396164</v>
       </c>
       <c r="R12" t="n">
-        <v>7063695</v>
+        <v>7063699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,15 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113610421</v>
+        <v>113610428</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>395880</v>
+        <v>396178</v>
       </c>
       <c r="R13" t="n">
-        <v>7063472</v>
+        <v>7063722</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,15 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113610427</v>
+        <v>113610429</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396164</v>
+        <v>396209</v>
       </c>
       <c r="R14" t="n">
-        <v>7063699</v>
+        <v>7063727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,15 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113610419</v>
+        <v>113610430</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>395926</v>
+        <v>396211</v>
       </c>
       <c r="R15" t="n">
-        <v>7063563</v>
+        <v>7063743</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2071,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,15 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113610430</v>
+        <v>113610431</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396211</v>
+        <v>396351</v>
       </c>
       <c r="R16" t="n">
-        <v>7063743</v>
+        <v>7063751</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2173,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 54055-2023 artfynd.xlsx
+++ b/artfynd/A 54055-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610419</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610420</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610421</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610422</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610424</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610427</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610428</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610429</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610430</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,8 +2272,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610431</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>